--- a/JavaApplication1/prueba.xlsx
+++ b/JavaApplication1/prueba.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="58">
   <si>
     <t>markIn</t>
   </si>
@@ -44,28 +44,40 @@
     <t>fps</t>
   </si>
   <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>17:15:50:635</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">jdsflkjdsklfjdsfkdsj  </t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>29.97d</t>
+  </si>
+  <si>
     <t>010</t>
   </si>
   <si>
     <t>16:51:17:577</t>
   </si>
   <si>
-    <t>na</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t xml:space="preserve"> muy importatante poco importante sdfdsfdsfdsf</t>
   </si>
   <si>
     <t>10</t>
-  </si>
-  <si>
-    <t>FALSE</t>
-  </si>
-  <si>
-    <t>29.97d</t>
   </si>
   <si>
     <t>009</t>
@@ -234,7 +246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -619,6 +631,41 @@
         <v>17</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="I12" t="n" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/JavaApplication1/prueba.xlsx
+++ b/JavaApplication1/prueba.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="50">
   <si>
     <t>markIn</t>
   </si>
@@ -44,10 +44,10 @@
     <t>fps</t>
   </si>
   <si>
-    <t>011</t>
-  </si>
-  <si>
-    <t>17:15:50:635</t>
+    <t>009</t>
+  </si>
+  <si>
+    <t>12:50:10:982</t>
   </si>
   <si>
     <t>na</t>
@@ -56,10 +56,10 @@
     <t/>
   </si>
   <si>
-    <t xml:space="preserve">jdsflkjdsklfjdsfkdsj  </t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>bjghbh  hjhg  hgjkhjhn</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>FALSE</t>
@@ -68,37 +68,13 @@
     <t>29.97d</t>
   </si>
   <si>
-    <t>010</t>
-  </si>
-  <si>
-    <t>16:51:17:577</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> muy importatante poco importante sdfdsfdsfdsf</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>009</t>
-  </si>
-  <si>
-    <t>16:51:04:551</t>
-  </si>
-  <si>
-    <t>jhfdh sjkd hdsjhkja</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>008</t>
   </si>
   <si>
-    <t>16:50:47:175</t>
-  </si>
-  <si>
-    <t>dsfd ds fsd</t>
+    <t>12:49:27:168</t>
+  </si>
+  <si>
+    <t>uj khg jkj kjh kjhk hk hk hj khg jhk j</t>
   </si>
   <si>
     <t>8</t>
@@ -246,7 +222,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -596,76 +572,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="F11" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G11" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H11" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="I11" t="n" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="K11" t="s" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>12</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E12" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="F12" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G12" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="I12" t="n" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="K12" t="s" s="2">
-        <v>17</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
